--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486325_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486325_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4973</v>
+        <v>7.7039</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5577</v>
+        <v>7.9493</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0604</v>
+        <v>-0.2454</v>
       </c>
       <c r="G2" t="n">
         <v>6.9455</v>
@@ -610,13 +610,13 @@
         <v>2.8276</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7193000000000001</v>
+        <v>0.4873</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9913999999999999</v>
+        <v>0.4002</v>
       </c>
       <c r="U2" t="n">
-        <v>0.272</v>
+        <v>0.0871</v>
       </c>
       <c r="V2" t="n">
         <v>-1.469</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.804</v>
+        <v>2.3457</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2047</v>
+        <v>2.8026</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4008</v>
+        <v>-0.4569</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6048</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2135</v>
+        <v>1.4295</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3913</v>
+        <v>-0.7284</v>
       </c>
       <c r="J3" t="n">
-        <v>2.581</v>
+        <v>1.9253</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5538</v>
+        <v>1.4663</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0272</v>
+        <v>0.459</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0238</v>
+        <v>-1.2241</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6597</v>
+        <v>-0.0368</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6359</v>
+        <v>-1.1873</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7419</v>
+        <v>0.5708</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7112</v>
+        <v>1.0094</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0306</v>
+        <v>-0.4386</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.3252</v>
+        <v>0.4212</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>-0.5342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6211</v>
+        <v>2.079</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4479</v>
+        <v>-0.4808</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8268</v>
+        <v>2.5598</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7010999999999999</v>
+        <v>1.3545</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4295</v>
+        <v>0.5289</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7284</v>
+        <v>0.8255</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9253</v>
+        <v>0.8327</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4663</v>
+        <v>0.2007</v>
       </c>
       <c r="L4" t="n">
-        <v>0.459</v>
+        <v>0.6319</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2241</v>
+        <v>0.5218</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0368</v>
+        <v>0.3282</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1873</v>
+        <v>0.1936</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8462</v>
+        <v>-0.024</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6548</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8085</v>
+        <v>-0.0156</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4212</v>
+        <v>-0.339</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5342</v>
+        <v>-0.339</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6867</v>
+        <v>1.8928</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9963</v>
+        <v>2.4477</v>
       </c>
       <c r="F5" t="n">
-        <v>2.683</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3545</v>
+        <v>2.6048</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5289</v>
+        <v>1.2135</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8255</v>
+        <v>1.3913</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8327</v>
+        <v>2.581</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2007</v>
+        <v>0.5538</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6319</v>
+        <v>2.0272</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5218</v>
+        <v>0.0238</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3282</v>
+        <v>0.6597</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1936</v>
+        <v>-0.6359</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4163</v>
+        <v>0.8307</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5239</v>
+        <v>0.9542</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1077</v>
+        <v>-0.1235</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.339</v>
+        <v>-1.3252</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.339</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5523</v>
+        <v>-0.2976</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3762</v>
+        <v>0.5384</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9285</v>
+        <v>-0.836</v>
       </c>
       <c r="G6" t="n">
         <v>0.1474</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6817</v>
+        <v>0.9364</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9217</v>
+        <v>1.0839</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.24</v>
+        <v>-0.1475</v>
       </c>
       <c r="V6" t="n">
         <v>-2.034</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.294</v>
+        <v>-1.1138</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9131</v>
+        <v>-1.7328</v>
       </c>
       <c r="F7" t="n">
         <v>0.619</v>
@@ -1000,10 +1000,10 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.286</v>
+        <v>-0.1057</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.137</v>
+        <v>0.0433</v>
       </c>
       <c r="U7" t="n">
         <v>-0.149</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3826</v>
+        <v>-1.5055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0813</v>
+        <v>0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4638</v>
+        <v>-1.5255</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5051</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>1.026</v>
+        <v>0.9031</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7114</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2533</v>
+        <v>0.1917</v>
       </c>
       <c r="V8" t="n">
         <v>-2.2085</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5533</v>
+        <v>-2.2668</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3879</v>
+        <v>-1.0706</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1654</v>
+        <v>-1.1962</v>
       </c>
       <c r="G9" t="n">
         <v>0.9191</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1455</v>
+        <v>0.1409</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.536</v>
+        <v>-0.2187</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3904</v>
+        <v>0.3596</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2393</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2477</v>
+        <v>-2.7639</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3334</v>
+        <v>-0.9729</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9143</v>
+        <v>-1.791</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7738</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6713</v>
+        <v>-0.1875</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6044</v>
+        <v>-0.2439</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6732</v>
+        <v>-5.5978</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0768</v>
+        <v>-3.9398</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5964</v>
+        <v>-1.6581</v>
       </c>
       <c r="G11" t="n">
         <v>0.108</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4761</v>
+        <v>-0.4008</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4675</v>
+        <v>-0.3305</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0703</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2599</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.375</v>
+        <v>-6.2324</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7212</v>
+        <v>-3.6094</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6538</v>
+        <v>-2.623</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9041</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2534</v>
+        <v>-0.1109</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.469</v>
+        <v>-5.7564</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2390999999999983</v>
+        <v>1.951700000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.7082</v>
+        <v>-7.708200000000001</v>
       </c>
       <c r="G13" t="n">
         <v>4.0244</v>
@@ -1468,13 +1468,13 @@
         <v>16.313</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3279</v>
+        <v>3.0403</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5262</v>
+        <v>3.2387</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1984999999999999</v>
+        <v>-0.1982</v>
       </c>
       <c r="V13" t="n">
         <v>-13.9089</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4289</v>
+        <v>5.5573</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5713</v>
+        <v>4.1243</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8575</v>
+        <v>1.433</v>
       </c>
       <c r="G14" t="n">
         <v>2.109</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2775</v>
+        <v>0.4059</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0227</v>
+        <v>0.5756</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7452</v>
+        <v>-0.1698</v>
       </c>
       <c r="V14" t="n">
         <v>2.8249</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0112</v>
+        <v>4.8549</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0978</v>
+        <v>4.0266</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9135</v>
+        <v>0.8283</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.872</v>
+        <v>3.9723</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2768</v>
+        <v>-0.447</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5953000000000001</v>
+        <v>4.4194</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2541</v>
+        <v>5.3853</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7696</v>
+        <v>0.3348</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5155999999999999</v>
+        <v>5.0505</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1261</v>
+        <v>-1.413</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0464</v>
+        <v>-0.7819</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.6312</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7639</v>
+        <v>-0.4612</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.3136</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0225</v>
+        <v>-0.1475</v>
       </c>
       <c r="V15" t="n">
-        <v>3.4721</v>
+        <v>1.5613</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5851</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.113</v>
+        <v>0.4313</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1633</v>
+        <v>4.6253</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2443</v>
+        <v>3.3213</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08110000000000001</v>
+        <v>1.304</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9723</v>
+        <v>-0.872</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.447</v>
+        <v>-0.2768</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4194</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3853</v>
+        <v>0.2541</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3348</v>
+        <v>0.7696</v>
       </c>
       <c r="L16" t="n">
-        <v>5.0505</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.413</v>
+        <v>-1.1261</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7819</v>
+        <v>-1.0464</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6312</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2175</v>
+        <v>2.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1528</v>
+        <v>-0.1499</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0959</v>
+        <v>-0.5179</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0569</v>
+        <v>0.368</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5613</v>
+        <v>3.4721</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>3.5851</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4313</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6312</v>
+        <v>2.2259</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2812</v>
+        <v>2.3929</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.65</v>
+        <v>-0.1671</v>
       </c>
       <c r="G17" t="n">
         <v>1.0043</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6782</v>
+        <v>-0.0835</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.125</v>
+        <v>-0.0132</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5533</v>
+        <v>-0.0703</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4125</v>
+        <v>-0.3021</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2623</v>
+        <v>-1.4858</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8497</v>
+        <v>1.1837</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9176</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1353</v>
+        <v>0.2457</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4026</v>
+        <v>0.1791</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2673</v>
+        <v>0.0667</v>
       </c>
       <c r="V18" t="n">
         <v>0.3698</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5414</v>
+        <v>-0.4026</v>
       </c>
       <c r="E19" t="n">
         <v>-0.1556</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3858</v>
+        <v>-0.247</v>
       </c>
       <c r="G19" t="n">
         <v>-3.512</v>
@@ -1936,13 +1936,13 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3461</v>
+        <v>-0.2073</v>
       </c>
       <c r="T19" t="n">
         <v>0.1406</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4867</v>
+        <v>-0.3479</v>
       </c>
       <c r="V19" t="n">
         <v>7.2318</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9798</v>
+        <v>-0.8718</v>
       </c>
       <c r="E20" t="n">
         <v>-0.09030000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8895</v>
+        <v>-0.7815</v>
       </c>
       <c r="G20" t="n">
         <v>-2.052</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0121</v>
+        <v>0.0958</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1454</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1332</v>
+        <v>0.2412</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8732</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2649</v>
+        <v>-2.0401</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2592</v>
+        <v>-3.1474</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9943</v>
+        <v>1.1073</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7613</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7792</v>
+        <v>1.004</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1454</v>
+        <v>-0.0336</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9246</v>
+        <v>1.0377</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7602</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5669</v>
+        <v>-3.1975</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.719</v>
+        <v>-1.2778</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8478</v>
+        <v>-1.9197</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9949</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4334</v>
+        <v>0.8027</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8857</v>
+        <v>0.3269</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5477</v>
+        <v>0.4759</v>
       </c>
       <c r="V22" t="n">
         <v>0.0822</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.469100000000001</v>
+        <v>10.4493</v>
       </c>
       <c r="E23" t="n">
         <v>7.708200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2392000000000003</v>
+        <v>2.741000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-4.024199999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.4505</v>
+        <v>-7.450500000000002</v>
       </c>
       <c r="I23" t="n">
         <v>3.426300000000001</v>
@@ -2224,22 +2224,22 @@
         <v>8.547499999999998</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2759000000000005</v>
+        <v>0.2759000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>8.271400000000002</v>
+        <v>8.2714</v>
       </c>
       <c r="M23" t="n">
         <v>-12.5717</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.726699999999999</v>
+        <v>-7.726700000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-4.8454</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0874</v>
+        <v>-1.087399999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.3131</v>
@@ -2248,13 +2248,13 @@
         <v>15.2255</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3277</v>
+        <v>1.6522</v>
       </c>
       <c r="T23" t="n">
         <v>0.1985</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5264</v>
+        <v>1.454</v>
       </c>
       <c r="V23" t="n">
         <v>13.9087</v>
